--- a/project/data/housing_dwellings_Toronto_2021_7.xlsx
+++ b/project/data/housing_dwellings_Toronto_2021_7.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexramiller/Library/CloudStorage/Dropbox/Git/ggr274/20261/project/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexramiller/Library/CloudStorage/Dropbox/Git/ggr274/20261/weekly-materials/week09/lecture/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{605EB229-94A6-AC4F-88D4-D1C36BB24C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDD02699-A54A-494E-87A2-141CDE9FF9F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="23860" windowHeight="17060" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="23860" windowHeight="17060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dwelling Characteristics" sheetId="11" r:id="rId1"/>
@@ -34,31 +34,7 @@
     <t>Living Alone (%)</t>
   </si>
   <si>
-    <t xml:space="preserve">  1 person</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  2 persons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  3 persons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  4 persons</t>
-  </si>
-  <si>
     <t>Total - Private households by household size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  1 person (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  2 persons (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  3 persons (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  4 persons (%)</t>
   </si>
   <si>
     <t>Number of Persons who are Lone-Parents</t>
@@ -714,13 +690,37 @@
     <t xml:space="preserve"> 2021 Census of Population - Socio-Demographic Variables (Dwelling - Structural Type of Dwelling) - City of Toronto Neighbourhoods</t>
   </si>
   <si>
-    <t xml:space="preserve">  5 or more persons</t>
+    <t>Number of Persons Living Alone</t>
   </si>
   <si>
-    <t xml:space="preserve">  5 or more persons (%)</t>
+    <t>1 person</t>
   </si>
   <si>
-    <t>Number of Persons Living Alone</t>
+    <t>1 person (%)</t>
+  </si>
+  <si>
+    <t>2 persons</t>
+  </si>
+  <si>
+    <t>2 persons (%)</t>
+  </si>
+  <si>
+    <t>3 persons</t>
+  </si>
+  <si>
+    <t>3 persons (%)</t>
+  </si>
+  <si>
+    <t>4 persons</t>
+  </si>
+  <si>
+    <t>4 persons (%)</t>
+  </si>
+  <si>
+    <t>5 or more persons</t>
+  </si>
+  <si>
+    <t>5 or more persons (%)</t>
   </si>
 </sst>
 </file>
@@ -1587,14 +1587,14 @@
     <xf numFmtId="0" fontId="23" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="43" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="19" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="19" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="43" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="46">
@@ -1933,7 +1933,7 @@
     <row r="1" spans="1:15" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="10"/>
       <c r="B1" s="1" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -1950,122 +1950,122 @@
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A2" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
+      <c r="A2" s="41" t="s">
+        <v>207</v>
+      </c>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
       <c r="O2" s="38"/>
     </row>
     <row r="3" spans="1:15" ht="29.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="40" t="s">
-        <v>214</v>
-      </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40"/>
+      <c r="A3" s="41" t="s">
+        <v>206</v>
+      </c>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="41"/>
       <c r="O3" s="38"/>
     </row>
     <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="40" t="s">
-        <v>213</v>
-      </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="40"/>
-      <c r="M4" s="40"/>
-      <c r="N4" s="40"/>
+      <c r="A4" s="41" t="s">
+        <v>205</v>
+      </c>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
       <c r="O4" s="38"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A5" s="40" t="s">
-        <v>212</v>
-      </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="40"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="40"/>
-      <c r="N5" s="40"/>
+      <c r="A5" s="41" t="s">
+        <v>204</v>
+      </c>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="41"/>
+      <c r="M5" s="41"/>
+      <c r="N5" s="41"/>
       <c r="O5" s="38"/>
     </row>
     <row r="6" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="40" t="s">
-        <v>211</v>
-      </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="40"/>
+      <c r="A6" s="41" t="s">
+        <v>203</v>
+      </c>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="41"/>
       <c r="O6" s="38"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A7" s="40" t="s">
-        <v>210</v>
-      </c>
-      <c r="B7" s="40"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="40"/>
-      <c r="K7" s="40"/>
-      <c r="L7" s="40"/>
-      <c r="M7" s="40"/>
-      <c r="N7" s="40"/>
+      <c r="A7" s="41" t="s">
+        <v>202</v>
+      </c>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="41"/>
+      <c r="M7" s="41"/>
+      <c r="N7" s="41"/>
       <c r="O7" s="20"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A8" s="21" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B8" s="20"/>
       <c r="C8" s="20"/>
@@ -2101,49 +2101,49 @@
     </row>
     <row r="10" spans="1:15" ht="29" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A10" s="22" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.15">
@@ -2151,7 +2151,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C11" s="24">
         <v>10720</v>
@@ -2198,7 +2198,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C12" s="25">
         <v>9730</v>
@@ -2245,7 +2245,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C13" s="25">
         <v>3230</v>
@@ -2292,7 +2292,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C14" s="25">
         <v>3945</v>
@@ -2339,7 +2339,7 @@
         <v>5</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C15" s="25">
         <v>3200</v>
@@ -2386,7 +2386,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C16" s="25">
         <v>7780</v>
@@ -2433,7 +2433,7 @@
         <v>7</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C17" s="25">
         <v>8585</v>
@@ -2480,7 +2480,7 @@
         <v>8</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C18" s="25">
         <v>4110</v>
@@ -2527,7 +2527,7 @@
         <v>9</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C19" s="25">
         <v>6290</v>
@@ -2574,7 +2574,7 @@
         <v>10</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C20" s="25">
         <v>3920</v>
@@ -2621,7 +2621,7 @@
         <v>11</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C21" s="25">
         <v>6855</v>
@@ -2668,7 +2668,7 @@
         <v>12</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C22" s="25">
         <v>4225</v>
@@ -2715,7 +2715,7 @@
         <v>13</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C23" s="25">
         <v>4735</v>
@@ -2762,7 +2762,7 @@
         <v>15</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C24" s="25">
         <v>3480</v>
@@ -2809,7 +2809,7 @@
         <v>16</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C25" s="25">
         <v>10505</v>
@@ -2856,7 +2856,7 @@
         <v>18</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C26" s="25">
         <v>5270</v>
@@ -2903,7 +2903,7 @@
         <v>19</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C27" s="25">
         <v>5290</v>
@@ -2950,7 +2950,7 @@
         <v>20</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C28" s="25">
         <v>4790</v>
@@ -2997,7 +2997,7 @@
         <v>21</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C29" s="25">
         <v>3930</v>
@@ -3044,7 +3044,7 @@
         <v>22</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C30" s="25">
         <v>5680</v>
@@ -3091,7 +3091,7 @@
         <v>23</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C31" s="25">
         <v>3915</v>
@@ -3138,7 +3138,7 @@
         <v>24</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C32" s="25">
         <v>7225</v>
@@ -3185,7 +3185,7 @@
         <v>25</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C33" s="25">
         <v>10010</v>
@@ -3232,7 +3232,7 @@
         <v>27</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C34" s="25">
         <v>10345</v>
@@ -3279,7 +3279,7 @@
         <v>28</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C35" s="25">
         <v>3520</v>
@@ -3326,7 +3326,7 @@
         <v>29</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C36" s="25">
         <v>3595</v>
@@ -3373,7 +3373,7 @@
         <v>30</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C37" s="25">
         <v>6400</v>
@@ -3420,7 +3420,7 @@
         <v>31</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C38" s="25">
         <v>6820</v>
@@ -3467,7 +3467,7 @@
         <v>32</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C39" s="25">
         <v>8175</v>
@@ -3514,7 +3514,7 @@
         <v>33</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C40" s="25">
         <v>7175</v>
@@ -3561,7 +3561,7 @@
         <v>34</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C41" s="25">
         <v>6055</v>
@@ -3608,7 +3608,7 @@
         <v>35</v>
       </c>
       <c r="B42" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C42" s="25">
         <v>10030</v>
@@ -3655,7 +3655,7 @@
         <v>36</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C43" s="25">
         <v>9095</v>
@@ -3702,7 +3702,7 @@
         <v>37</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C44" s="25">
         <v>7830</v>
@@ -3749,7 +3749,7 @@
         <v>38</v>
       </c>
       <c r="B45" s="23" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C45" s="25">
         <v>6555</v>
@@ -3796,7 +3796,7 @@
         <v>39</v>
       </c>
       <c r="B46" s="23" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C46" s="25">
         <v>8340</v>
@@ -3843,7 +3843,7 @@
         <v>40</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C47" s="25">
         <v>6325</v>
@@ -3890,7 +3890,7 @@
         <v>41</v>
       </c>
       <c r="B48" s="23" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C48" s="25">
         <v>3300</v>
@@ -3937,7 +3937,7 @@
         <v>42</v>
       </c>
       <c r="B49" s="23" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C49" s="25">
         <v>12210</v>
@@ -3984,7 +3984,7 @@
         <v>43</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C50" s="25">
         <v>7275</v>
@@ -4031,7 +4031,7 @@
         <v>44</v>
       </c>
       <c r="B51" s="23" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C51" s="25">
         <v>8165</v>
@@ -4078,7 +4078,7 @@
         <v>46</v>
       </c>
       <c r="B52" s="23" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C52" s="25">
         <v>5460</v>
@@ -4125,7 +4125,7 @@
         <v>47</v>
       </c>
       <c r="B53" s="23" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C53" s="25">
         <v>10225</v>
@@ -4172,7 +4172,7 @@
         <v>48</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C54" s="25">
         <v>6380</v>
@@ -4219,7 +4219,7 @@
         <v>49</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C55" s="25">
         <v>4765</v>
@@ -4266,7 +4266,7 @@
         <v>50</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C56" s="25">
         <v>6155</v>
@@ -4313,7 +4313,7 @@
         <v>52</v>
       </c>
       <c r="B57" s="23" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C57" s="25">
         <v>10455</v>
@@ -4360,7 +4360,7 @@
         <v>53</v>
       </c>
       <c r="B58" s="23" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C58" s="25">
         <v>8515</v>
@@ -4407,7 +4407,7 @@
         <v>54</v>
       </c>
       <c r="B59" s="23" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C59" s="25">
         <v>7465</v>
@@ -4454,7 +4454,7 @@
         <v>55</v>
       </c>
       <c r="B60" s="23" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C60" s="25">
         <v>7065</v>
@@ -4501,7 +4501,7 @@
         <v>56</v>
       </c>
       <c r="B61" s="23" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C61" s="25">
         <v>6430</v>
@@ -4548,7 +4548,7 @@
         <v>57</v>
       </c>
       <c r="B62" s="23" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C62" s="25">
         <v>5300</v>
@@ -4595,7 +4595,7 @@
         <v>58</v>
       </c>
       <c r="B63" s="23" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C63" s="25">
         <v>3735</v>
@@ -4642,7 +4642,7 @@
         <v>59</v>
       </c>
       <c r="B64" s="23" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C64" s="25">
         <v>6945</v>
@@ -4689,7 +4689,7 @@
         <v>60</v>
       </c>
       <c r="B65" s="23" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C65" s="25">
         <v>3370</v>
@@ -4736,7 +4736,7 @@
         <v>61</v>
       </c>
       <c r="B66" s="23" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C66" s="25">
         <v>6010</v>
@@ -4783,7 +4783,7 @@
         <v>62</v>
       </c>
       <c r="B67" s="23" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C67" s="25">
         <v>9485</v>
@@ -4830,7 +4830,7 @@
         <v>63</v>
       </c>
       <c r="B68" s="23" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C68" s="25">
         <v>9445</v>
@@ -4877,7 +4877,7 @@
         <v>64</v>
       </c>
       <c r="B69" s="23" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C69" s="25">
         <v>5230</v>
@@ -4924,7 +4924,7 @@
         <v>65</v>
       </c>
       <c r="B70" s="23" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C70" s="25">
         <v>6025</v>
@@ -4971,7 +4971,7 @@
         <v>66</v>
       </c>
       <c r="B71" s="23" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C71" s="25">
         <v>3910</v>
@@ -5018,7 +5018,7 @@
         <v>67</v>
       </c>
       <c r="B72" s="23" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C72" s="25">
         <v>3640</v>
@@ -5065,7 +5065,7 @@
         <v>68</v>
       </c>
       <c r="B73" s="23" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C73" s="25">
         <v>4910</v>
@@ -5112,7 +5112,7 @@
         <v>69</v>
       </c>
       <c r="B74" s="23" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C74" s="25">
         <v>3095</v>
@@ -5159,7 +5159,7 @@
         <v>70</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C75" s="25">
         <v>12725</v>
@@ -5206,7 +5206,7 @@
         <v>71</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C76" s="25">
         <v>6195</v>
@@ -5253,7 +5253,7 @@
         <v>72</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C77" s="25">
         <v>6115</v>
@@ -5300,7 +5300,7 @@
         <v>73</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C78" s="25">
         <v>13285</v>
@@ -5347,7 +5347,7 @@
         <v>74</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C79" s="25">
         <v>9535</v>
@@ -5394,7 +5394,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C80" s="25">
         <v>9525</v>
@@ -5441,7 +5441,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C81" s="25">
         <v>3245</v>
@@ -5488,7 +5488,7 @@
         <v>80</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C82" s="25">
         <v>6165</v>
@@ -5535,7 +5535,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="23" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C83" s="25">
         <v>6835</v>
@@ -5582,7 +5582,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="23" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C84" s="25">
         <v>5265</v>
@@ -5629,7 +5629,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="23" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C85" s="25">
         <v>7885</v>
@@ -5676,7 +5676,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="23" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C86" s="25">
         <v>11285</v>
@@ -5723,7 +5723,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="23" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C87" s="25">
         <v>6795</v>
@@ -5770,7 +5770,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="23" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C88" s="25">
         <v>10440</v>
@@ -5817,7 +5817,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="23" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C89" s="25">
         <v>11100</v>
@@ -5864,7 +5864,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="23" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C90" s="25">
         <v>3825</v>
@@ -5911,7 +5911,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="23" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C91" s="25">
         <v>6020</v>
@@ -5958,7 +5958,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="23" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C92" s="25">
         <v>4200</v>
@@ -6005,7 +6005,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="23" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C93" s="25">
         <v>5200</v>
@@ -6052,7 +6052,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="23" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C94" s="25">
         <v>5790</v>
@@ -6099,7 +6099,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="23" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C95" s="25">
         <v>16325</v>
@@ -6146,7 +6146,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="23" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C96" s="25">
         <v>5750</v>
@@ -6193,7 +6193,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="23" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C97" s="25">
         <v>7225</v>
@@ -6240,7 +6240,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="23" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C98" s="25">
         <v>9895</v>
@@ -6287,7 +6287,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="23" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C99" s="25">
         <v>7170</v>
@@ -6334,7 +6334,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="23" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C100" s="25">
         <v>6000</v>
@@ -6381,7 +6381,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="23" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C101" s="25">
         <v>5125</v>
@@ -6428,7 +6428,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="23" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C102" s="25">
         <v>5235</v>
@@ -6475,7 +6475,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="23" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C103" s="25">
         <v>5795</v>
@@ -6522,7 +6522,7 @@
         <v>105</v>
       </c>
       <c r="B104" s="23" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C104" s="25">
         <v>5465</v>
@@ -6569,7 +6569,7 @@
         <v>106</v>
       </c>
       <c r="B105" s="23" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C105" s="25">
         <v>6355</v>
@@ -6616,7 +6616,7 @@
         <v>107</v>
       </c>
       <c r="B106" s="23" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C106" s="25">
         <v>8650</v>
@@ -6663,7 +6663,7 @@
         <v>108</v>
       </c>
       <c r="B107" s="23" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C107" s="25">
         <v>5945</v>
@@ -6710,7 +6710,7 @@
         <v>109</v>
       </c>
       <c r="B108" s="23" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C108" s="25">
         <v>3705</v>
@@ -6757,7 +6757,7 @@
         <v>110</v>
       </c>
       <c r="B109" s="23" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C109" s="25">
         <v>4370</v>
@@ -6804,7 +6804,7 @@
         <v>111</v>
       </c>
       <c r="B110" s="23" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C110" s="25">
         <v>9030</v>
@@ -6851,7 +6851,7 @@
         <v>112</v>
       </c>
       <c r="B111" s="23" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C111" s="25">
         <v>2575</v>
@@ -6898,7 +6898,7 @@
         <v>113</v>
       </c>
       <c r="B112" s="23" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C112" s="25">
         <v>7915</v>
@@ -6945,7 +6945,7 @@
         <v>114</v>
       </c>
       <c r="B113" s="23" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C113" s="25">
         <v>3110</v>
@@ -6992,7 +6992,7 @@
         <v>115</v>
       </c>
       <c r="B114" s="23" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="C114" s="25">
         <v>5060</v>
@@ -7039,7 +7039,7 @@
         <v>116</v>
       </c>
       <c r="B115" s="23" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C115" s="25">
         <v>7855</v>
@@ -7086,7 +7086,7 @@
         <v>118</v>
       </c>
       <c r="B116" s="23" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C116" s="25">
         <v>10350</v>
@@ -7133,7 +7133,7 @@
         <v>119</v>
       </c>
       <c r="B117" s="23" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C117" s="25">
         <v>10285</v>
@@ -7180,7 +7180,7 @@
         <v>120</v>
       </c>
       <c r="B118" s="23" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C118" s="25">
         <v>9395</v>
@@ -7227,7 +7227,7 @@
         <v>121</v>
       </c>
       <c r="B119" s="23" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C119" s="25">
         <v>5330</v>
@@ -7274,7 +7274,7 @@
         <v>122</v>
       </c>
       <c r="B120" s="23" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C120" s="25">
         <v>9615</v>
@@ -7321,7 +7321,7 @@
         <v>123</v>
       </c>
       <c r="B121" s="23" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C121" s="25">
         <v>5860</v>
@@ -7368,7 +7368,7 @@
         <v>124</v>
       </c>
       <c r="B122" s="23" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C122" s="25">
         <v>6595</v>
@@ -7415,7 +7415,7 @@
         <v>125</v>
       </c>
       <c r="B123" s="23" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C123" s="25">
         <v>4975</v>
@@ -7462,7 +7462,7 @@
         <v>126</v>
       </c>
       <c r="B124" s="23" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C124" s="25">
         <v>8735</v>
@@ -7509,7 +7509,7 @@
         <v>128</v>
       </c>
       <c r="B125" s="23" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C125" s="25">
         <v>8885</v>
@@ -7556,7 +7556,7 @@
         <v>129</v>
       </c>
       <c r="B126" s="23" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C126" s="25">
         <v>9095</v>
@@ -7603,7 +7603,7 @@
         <v>130</v>
       </c>
       <c r="B127" s="23" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C127" s="25">
         <v>7580</v>
@@ -7650,7 +7650,7 @@
         <v>133</v>
       </c>
       <c r="B128" s="23" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C128" s="25">
         <v>4430</v>
@@ -7697,7 +7697,7 @@
         <v>134</v>
       </c>
       <c r="B129" s="23" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C129" s="25">
         <v>3785</v>
@@ -7744,7 +7744,7 @@
         <v>135</v>
       </c>
       <c r="B130" s="23" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C130" s="25">
         <v>5885</v>
@@ -7791,7 +7791,7 @@
         <v>136</v>
       </c>
       <c r="B131" s="23" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C131" s="25">
         <v>10165</v>
@@ -7838,7 +7838,7 @@
         <v>138</v>
       </c>
       <c r="B132" s="23" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C132" s="25">
         <v>8185</v>
@@ -7885,7 +7885,7 @@
         <v>139</v>
       </c>
       <c r="B133" s="23" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C133" s="25">
         <v>5955</v>
@@ -7932,7 +7932,7 @@
         <v>140</v>
       </c>
       <c r="B134" s="23" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C134" s="25">
         <v>3940</v>
@@ -7979,7 +7979,7 @@
         <v>141</v>
       </c>
       <c r="B135" s="23" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C135" s="25">
         <v>8835</v>
@@ -8026,7 +8026,7 @@
         <v>142</v>
       </c>
       <c r="B136" s="23" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C136" s="25">
         <v>9800</v>
@@ -8073,7 +8073,7 @@
         <v>143</v>
       </c>
       <c r="B137" s="23" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C137" s="25">
         <v>7020</v>
@@ -8120,7 +8120,7 @@
         <v>144</v>
       </c>
       <c r="B138" s="23" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="C138" s="25">
         <v>6545</v>
@@ -8167,7 +8167,7 @@
         <v>145</v>
       </c>
       <c r="B139" s="23" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="C139" s="25">
         <v>5125</v>
@@ -8214,7 +8214,7 @@
         <v>146</v>
       </c>
       <c r="B140" s="23" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="C140" s="25">
         <v>8565</v>
@@ -8261,7 +8261,7 @@
         <v>147</v>
       </c>
       <c r="B141" s="23" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C141" s="25">
         <v>8290</v>
@@ -8308,7 +8308,7 @@
         <v>148</v>
       </c>
       <c r="B142" s="23" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="C142" s="25">
         <v>7210</v>
@@ -8355,7 +8355,7 @@
         <v>149</v>
       </c>
       <c r="B143" s="23" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C143" s="25">
         <v>5050</v>
@@ -8402,7 +8402,7 @@
         <v>150</v>
       </c>
       <c r="B144" s="23" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C144" s="25">
         <v>8135</v>
@@ -8449,7 +8449,7 @@
         <v>151</v>
       </c>
       <c r="B145" s="23" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C145" s="25">
         <v>9840</v>
@@ -8496,7 +8496,7 @@
         <v>152</v>
       </c>
       <c r="B146" s="23" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C146" s="25">
         <v>5610</v>
@@ -8543,7 +8543,7 @@
         <v>153</v>
       </c>
       <c r="B147" s="23" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C147" s="25">
         <v>6995</v>
@@ -8590,7 +8590,7 @@
         <v>154</v>
       </c>
       <c r="B148" s="23" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="C148" s="25">
         <v>7695</v>
@@ -8637,7 +8637,7 @@
         <v>155</v>
       </c>
       <c r="B149" s="23" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C149" s="25">
         <v>6945</v>
@@ -8684,7 +8684,7 @@
         <v>156</v>
       </c>
       <c r="B150" s="23" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C150" s="25">
         <v>7415</v>
@@ -8731,7 +8731,7 @@
         <v>157</v>
       </c>
       <c r="B151" s="23" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="C151" s="25">
         <v>3365</v>
@@ -8778,7 +8778,7 @@
         <v>158</v>
       </c>
       <c r="B152" s="23" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C152" s="25">
         <v>9265</v>
@@ -8825,7 +8825,7 @@
         <v>159</v>
       </c>
       <c r="B153" s="23" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C153" s="25">
         <v>11920</v>
@@ -8872,7 +8872,7 @@
         <v>160</v>
       </c>
       <c r="B154" s="23" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C154" s="25">
         <v>7870</v>
@@ -8919,7 +8919,7 @@
         <v>161</v>
       </c>
       <c r="B155" s="23" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C155" s="25">
         <v>13325</v>
@@ -8966,7 +8966,7 @@
         <v>162</v>
       </c>
       <c r="B156" s="23" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C156" s="25">
         <v>7615</v>
@@ -9013,7 +9013,7 @@
         <v>163</v>
       </c>
       <c r="B157" s="23" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C157" s="25">
         <v>12495</v>
@@ -9060,7 +9060,7 @@
         <v>164</v>
       </c>
       <c r="B158" s="23" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C158" s="25">
         <v>17070</v>
@@ -9107,7 +9107,7 @@
         <v>165</v>
       </c>
       <c r="B159" s="23" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C159" s="25">
         <v>16545</v>
@@ -9154,7 +9154,7 @@
         <v>166</v>
       </c>
       <c r="B160" s="23" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C160" s="25">
         <v>18780</v>
@@ -9201,7 +9201,7 @@
         <v>167</v>
       </c>
       <c r="B161" s="23" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C161" s="25">
         <v>14610</v>
@@ -9248,7 +9248,7 @@
         <v>168</v>
       </c>
       <c r="B162" s="23" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="C162" s="25">
         <v>11095</v>
@@ -9295,7 +9295,7 @@
         <v>169</v>
       </c>
       <c r="B163" s="23" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C163" s="25">
         <v>10590</v>
@@ -9342,7 +9342,7 @@
         <v>170</v>
       </c>
       <c r="B164" s="23" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C164" s="25">
         <v>7455</v>
@@ -9389,7 +9389,7 @@
         <v>171</v>
       </c>
       <c r="B165" s="23" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C165" s="25">
         <v>10225</v>
@@ -9436,7 +9436,7 @@
         <v>172</v>
       </c>
       <c r="B166" s="23" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C166" s="25">
         <v>5255</v>
@@ -9483,7 +9483,7 @@
         <v>173</v>
       </c>
       <c r="B167" s="23" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="C167" s="25">
         <v>9430</v>
@@ -9530,7 +9530,7 @@
         <v>174</v>
       </c>
       <c r="B168" s="23" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C168" s="25">
         <v>13185</v>
@@ -9575,7 +9575,7 @@
     <row r="169" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A169" s="11"/>
       <c r="B169" s="12" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C169" s="13">
         <v>1160890</v>
@@ -9647,7 +9647,7 @@
     <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="10"/>
       <c r="B1" s="1" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="2"/>
@@ -9662,76 +9662,76 @@
       <c r="M1" s="10"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="41" t="s">
-        <v>186</v>
-      </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
+      <c r="A2" s="42" t="s">
+        <v>178</v>
+      </c>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="42"/>
     </row>
     <row r="3" spans="1:13" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="40" t="s">
-        <v>185</v>
-      </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
+      <c r="A3" s="41" t="s">
+        <v>177</v>
+      </c>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="40" t="s">
-        <v>184</v>
-      </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="40"/>
-      <c r="M4" s="40"/>
+      <c r="A4" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
     </row>
     <row r="5" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="40" t="s">
-        <v>187</v>
-      </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="40"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="40"/>
+      <c r="A5" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="41"/>
+      <c r="M5" s="41"/>
     </row>
     <row r="6" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="21" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="20"/>
@@ -9762,43 +9762,43 @@
     </row>
     <row r="8" spans="1:13" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>3</v>
+        <v>210</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>8</v>
+        <v>211</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>4</v>
+        <v>212</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>9</v>
+        <v>213</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>5</v>
+        <v>214</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>10</v>
+        <v>215</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>6</v>
+        <v>216</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>11</v>
+        <v>217</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M8" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
@@ -9806,7 +9806,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C9" s="24">
         <v>10695</v>
@@ -9847,7 +9847,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C10" s="25">
         <v>9745</v>
@@ -9888,7 +9888,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C11" s="25">
         <v>3240</v>
@@ -9929,7 +9929,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C12" s="25">
         <v>3945</v>
@@ -9970,7 +9970,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C13" s="25">
         <v>3195</v>
@@ -10011,7 +10011,7 @@
         <v>6</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C14" s="25">
         <v>7780</v>
@@ -10052,7 +10052,7 @@
         <v>7</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C15" s="25">
         <v>8585</v>
@@ -10093,7 +10093,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C16" s="25">
         <v>4110</v>
@@ -10134,7 +10134,7 @@
         <v>9</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C17" s="25">
         <v>6285</v>
@@ -10175,7 +10175,7 @@
         <v>10</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C18" s="25">
         <v>3880</v>
@@ -10216,7 +10216,7 @@
         <v>11</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C19" s="25">
         <v>6855</v>
@@ -10257,7 +10257,7 @@
         <v>12</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C20" s="25">
         <v>4215</v>
@@ -10298,7 +10298,7 @@
         <v>13</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C21" s="25">
         <v>4730</v>
@@ -10339,7 +10339,7 @@
         <v>15</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C22" s="25">
         <v>3470</v>
@@ -10380,7 +10380,7 @@
         <v>16</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C23" s="25">
         <v>10500</v>
@@ -10421,7 +10421,7 @@
         <v>18</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C24" s="25">
         <v>5280</v>
@@ -10462,7 +10462,7 @@
         <v>19</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C25" s="25">
         <v>5285</v>
@@ -10503,7 +10503,7 @@
         <v>20</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C26" s="25">
         <v>4790</v>
@@ -10544,7 +10544,7 @@
         <v>21</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C27" s="25">
         <v>3930</v>
@@ -10585,7 +10585,7 @@
         <v>22</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C28" s="25">
         <v>5695</v>
@@ -10626,7 +10626,7 @@
         <v>23</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C29" s="25">
         <v>3925</v>
@@ -10667,7 +10667,7 @@
         <v>24</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C30" s="25">
         <v>7230</v>
@@ -10708,7 +10708,7 @@
         <v>25</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C31" s="25">
         <v>10005</v>
@@ -10749,7 +10749,7 @@
         <v>27</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C32" s="25">
         <v>10365</v>
@@ -10790,7 +10790,7 @@
         <v>28</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C33" s="25">
         <v>3515</v>
@@ -10831,7 +10831,7 @@
         <v>29</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C34" s="25">
         <v>3605</v>
@@ -10872,7 +10872,7 @@
         <v>30</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C35" s="25">
         <v>6400</v>
@@ -10913,7 +10913,7 @@
         <v>31</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C36" s="25">
         <v>6845</v>
@@ -10954,7 +10954,7 @@
         <v>32</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C37" s="25">
         <v>8165</v>
@@ -10995,7 +10995,7 @@
         <v>33</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C38" s="25">
         <v>7140</v>
@@ -11036,7 +11036,7 @@
         <v>34</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C39" s="25">
         <v>6055</v>
@@ -11077,7 +11077,7 @@
         <v>35</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C40" s="25">
         <v>10045</v>
@@ -11118,7 +11118,7 @@
         <v>36</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C41" s="25">
         <v>9105</v>
@@ -11159,7 +11159,7 @@
         <v>37</v>
       </c>
       <c r="B42" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C42" s="25">
         <v>7840</v>
@@ -11200,7 +11200,7 @@
         <v>38</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C43" s="25">
         <v>6560</v>
@@ -11241,7 +11241,7 @@
         <v>39</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C44" s="25">
         <v>8325</v>
@@ -11282,7 +11282,7 @@
         <v>40</v>
       </c>
       <c r="B45" s="23" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C45" s="25">
         <v>6345</v>
@@ -11323,7 +11323,7 @@
         <v>41</v>
       </c>
       <c r="B46" s="23" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C46" s="25">
         <v>3295</v>
@@ -11364,7 +11364,7 @@
         <v>42</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C47" s="25">
         <v>12205</v>
@@ -11405,7 +11405,7 @@
         <v>43</v>
       </c>
       <c r="B48" s="23" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C48" s="25">
         <v>7285</v>
@@ -11446,7 +11446,7 @@
         <v>44</v>
       </c>
       <c r="B49" s="23" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C49" s="25">
         <v>8200</v>
@@ -11487,7 +11487,7 @@
         <v>46</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C50" s="25">
         <v>5445</v>
@@ -11528,7 +11528,7 @@
         <v>47</v>
       </c>
       <c r="B51" s="23" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C51" s="25">
         <v>10250</v>
@@ -11569,7 +11569,7 @@
         <v>48</v>
       </c>
       <c r="B52" s="23" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C52" s="25">
         <v>6380</v>
@@ -11610,7 +11610,7 @@
         <v>49</v>
       </c>
       <c r="B53" s="23" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C53" s="25">
         <v>4740</v>
@@ -11651,7 +11651,7 @@
         <v>50</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C54" s="25">
         <v>6145</v>
@@ -11692,7 +11692,7 @@
         <v>52</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C55" s="25">
         <v>10485</v>
@@ -11733,7 +11733,7 @@
         <v>53</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C56" s="25">
         <v>8510</v>
@@ -11774,7 +11774,7 @@
         <v>54</v>
       </c>
       <c r="B57" s="23" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C57" s="25">
         <v>7470</v>
@@ -11815,7 +11815,7 @@
         <v>55</v>
       </c>
       <c r="B58" s="23" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C58" s="25">
         <v>7055</v>
@@ -11856,7 +11856,7 @@
         <v>56</v>
       </c>
       <c r="B59" s="23" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C59" s="25">
         <v>6430</v>
@@ -11897,7 +11897,7 @@
         <v>57</v>
       </c>
       <c r="B60" s="23" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C60" s="25">
         <v>5260</v>
@@ -11938,7 +11938,7 @@
         <v>58</v>
       </c>
       <c r="B61" s="23" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C61" s="25">
         <v>3730</v>
@@ -11979,7 +11979,7 @@
         <v>59</v>
       </c>
       <c r="B62" s="23" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C62" s="25">
         <v>6930</v>
@@ -12020,7 +12020,7 @@
         <v>60</v>
       </c>
       <c r="B63" s="23" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C63" s="25">
         <v>3380</v>
@@ -12061,7 +12061,7 @@
         <v>61</v>
       </c>
       <c r="B64" s="23" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C64" s="25">
         <v>6005</v>
@@ -12102,7 +12102,7 @@
         <v>62</v>
       </c>
       <c r="B65" s="23" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C65" s="25">
         <v>9480</v>
@@ -12143,7 +12143,7 @@
         <v>63</v>
       </c>
       <c r="B66" s="23" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C66" s="25">
         <v>9420</v>
@@ -12184,7 +12184,7 @@
         <v>64</v>
       </c>
       <c r="B67" s="23" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C67" s="25">
         <v>5235</v>
@@ -12225,7 +12225,7 @@
         <v>65</v>
       </c>
       <c r="B68" s="23" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C68" s="25">
         <v>6030</v>
@@ -12266,7 +12266,7 @@
         <v>66</v>
       </c>
       <c r="B69" s="23" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C69" s="25">
         <v>3915</v>
@@ -12307,7 +12307,7 @@
         <v>67</v>
       </c>
       <c r="B70" s="23" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C70" s="25">
         <v>3645</v>
@@ -12348,7 +12348,7 @@
         <v>68</v>
       </c>
       <c r="B71" s="23" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C71" s="25">
         <v>4900</v>
@@ -12389,7 +12389,7 @@
         <v>69</v>
       </c>
       <c r="B72" s="23" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C72" s="25">
         <v>3105</v>
@@ -12430,7 +12430,7 @@
         <v>70</v>
       </c>
       <c r="B73" s="23" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C73" s="25">
         <v>12690</v>
@@ -12471,7 +12471,7 @@
         <v>71</v>
       </c>
       <c r="B74" s="23" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C74" s="25">
         <v>6195</v>
@@ -12512,7 +12512,7 @@
         <v>72</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C75" s="25">
         <v>6105</v>
@@ -12553,7 +12553,7 @@
         <v>73</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C76" s="25">
         <v>13280</v>
@@ -12594,7 +12594,7 @@
         <v>74</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C77" s="25">
         <v>9525</v>
@@ -12635,7 +12635,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C78" s="25">
         <v>9515</v>
@@ -12676,7 +12676,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C79" s="25">
         <v>3240</v>
@@ -12717,7 +12717,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C80" s="25">
         <v>6200</v>
@@ -12758,7 +12758,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C81" s="25">
         <v>6850</v>
@@ -12799,7 +12799,7 @@
         <v>83</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C82" s="25">
         <v>5275</v>
@@ -12840,7 +12840,7 @@
         <v>84</v>
       </c>
       <c r="B83" s="23" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C83" s="25">
         <v>7910</v>
@@ -12881,7 +12881,7 @@
         <v>85</v>
       </c>
       <c r="B84" s="23" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C84" s="25">
         <v>11275</v>
@@ -12922,7 +12922,7 @@
         <v>86</v>
       </c>
       <c r="B85" s="23" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C85" s="25">
         <v>6780</v>
@@ -12963,7 +12963,7 @@
         <v>87</v>
       </c>
       <c r="B86" s="23" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C86" s="25">
         <v>10450</v>
@@ -13004,7 +13004,7 @@
         <v>88</v>
       </c>
       <c r="B87" s="23" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C87" s="25">
         <v>11100</v>
@@ -13045,7 +13045,7 @@
         <v>89</v>
       </c>
       <c r="B88" s="23" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C88" s="25">
         <v>3835</v>
@@ -13086,7 +13086,7 @@
         <v>90</v>
       </c>
       <c r="B89" s="23" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C89" s="25">
         <v>6030</v>
@@ -13127,7 +13127,7 @@
         <v>91</v>
       </c>
       <c r="B90" s="23" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C90" s="25">
         <v>4205</v>
@@ -13168,7 +13168,7 @@
         <v>92</v>
       </c>
       <c r="B91" s="23" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C91" s="25">
         <v>5205</v>
@@ -13209,7 +13209,7 @@
         <v>94</v>
       </c>
       <c r="B92" s="23" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C92" s="25">
         <v>5790</v>
@@ -13250,7 +13250,7 @@
         <v>95</v>
       </c>
       <c r="B93" s="23" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C93" s="25">
         <v>16320</v>
@@ -13291,7 +13291,7 @@
         <v>96</v>
       </c>
       <c r="B94" s="23" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C94" s="25">
         <v>5745</v>
@@ -13332,7 +13332,7 @@
         <v>97</v>
       </c>
       <c r="B95" s="23" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C95" s="25">
         <v>7220</v>
@@ -13373,7 +13373,7 @@
         <v>98</v>
       </c>
       <c r="B96" s="23" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C96" s="25">
         <v>9870</v>
@@ -13414,7 +13414,7 @@
         <v>99</v>
       </c>
       <c r="B97" s="23" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C97" s="25">
         <v>7165</v>
@@ -13455,7 +13455,7 @@
         <v>100</v>
       </c>
       <c r="B98" s="23" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C98" s="25">
         <v>5990</v>
@@ -13496,7 +13496,7 @@
         <v>101</v>
       </c>
       <c r="B99" s="23" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C99" s="25">
         <v>5125</v>
@@ -13537,7 +13537,7 @@
         <v>102</v>
       </c>
       <c r="B100" s="23" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C100" s="25">
         <v>5245</v>
@@ -13578,7 +13578,7 @@
         <v>103</v>
       </c>
       <c r="B101" s="23" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C101" s="25">
         <v>5785</v>
@@ -13619,7 +13619,7 @@
         <v>105</v>
       </c>
       <c r="B102" s="23" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C102" s="25">
         <v>5470</v>
@@ -13660,7 +13660,7 @@
         <v>106</v>
       </c>
       <c r="B103" s="23" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C103" s="25">
         <v>6320</v>
@@ -13701,7 +13701,7 @@
         <v>107</v>
       </c>
       <c r="B104" s="23" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C104" s="25">
         <v>8650</v>
@@ -13742,7 +13742,7 @@
         <v>108</v>
       </c>
       <c r="B105" s="23" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C105" s="25">
         <v>5950</v>
@@ -13783,7 +13783,7 @@
         <v>109</v>
       </c>
       <c r="B106" s="23" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C106" s="25">
         <v>3720</v>
@@ -13824,7 +13824,7 @@
         <v>110</v>
       </c>
       <c r="B107" s="23" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C107" s="25">
         <v>4380</v>
@@ -13865,7 +13865,7 @@
         <v>111</v>
       </c>
       <c r="B108" s="23" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C108" s="25">
         <v>9030</v>
@@ -13906,7 +13906,7 @@
         <v>112</v>
       </c>
       <c r="B109" s="23" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C109" s="25">
         <v>2565</v>
@@ -13947,7 +13947,7 @@
         <v>113</v>
       </c>
       <c r="B110" s="23" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C110" s="25">
         <v>7905</v>
@@ -13988,7 +13988,7 @@
         <v>114</v>
       </c>
       <c r="B111" s="23" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C111" s="25">
         <v>3105</v>
@@ -14029,7 +14029,7 @@
         <v>115</v>
       </c>
       <c r="B112" s="23" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="C112" s="25">
         <v>5050</v>
@@ -14070,7 +14070,7 @@
         <v>116</v>
       </c>
       <c r="B113" s="23" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C113" s="25">
         <v>7860</v>
@@ -14111,7 +14111,7 @@
         <v>118</v>
       </c>
       <c r="B114" s="23" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C114" s="25">
         <v>10360</v>
@@ -14152,7 +14152,7 @@
         <v>119</v>
       </c>
       <c r="B115" s="23" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C115" s="25">
         <v>10270</v>
@@ -14193,7 +14193,7 @@
         <v>120</v>
       </c>
       <c r="B116" s="23" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C116" s="25">
         <v>9390</v>
@@ -14234,7 +14234,7 @@
         <v>121</v>
       </c>
       <c r="B117" s="23" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C117" s="25">
         <v>5315</v>
@@ -14275,7 +14275,7 @@
         <v>122</v>
       </c>
       <c r="B118" s="23" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C118" s="25">
         <v>9615</v>
@@ -14316,7 +14316,7 @@
         <v>123</v>
       </c>
       <c r="B119" s="23" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C119" s="25">
         <v>5905</v>
@@ -14357,7 +14357,7 @@
         <v>124</v>
       </c>
       <c r="B120" s="23" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C120" s="25">
         <v>6590</v>
@@ -14398,7 +14398,7 @@
         <v>125</v>
       </c>
       <c r="B121" s="23" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C121" s="25">
         <v>4965</v>
@@ -14439,7 +14439,7 @@
         <v>126</v>
       </c>
       <c r="B122" s="23" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C122" s="25">
         <v>8715</v>
@@ -14480,7 +14480,7 @@
         <v>128</v>
       </c>
       <c r="B123" s="23" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C123" s="25">
         <v>8870</v>
@@ -14521,7 +14521,7 @@
         <v>129</v>
       </c>
       <c r="B124" s="23" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C124" s="25">
         <v>9105</v>
@@ -14562,7 +14562,7 @@
         <v>130</v>
       </c>
       <c r="B125" s="23" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C125" s="25">
         <v>7585</v>
@@ -14603,7 +14603,7 @@
         <v>133</v>
       </c>
       <c r="B126" s="23" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C126" s="25">
         <v>4410</v>
@@ -14644,7 +14644,7 @@
         <v>134</v>
       </c>
       <c r="B127" s="23" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C127" s="25">
         <v>3795</v>
@@ -14685,7 +14685,7 @@
         <v>135</v>
       </c>
       <c r="B128" s="23" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C128" s="25">
         <v>5875</v>
@@ -14726,7 +14726,7 @@
         <v>136</v>
       </c>
       <c r="B129" s="23" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C129" s="25">
         <v>10155</v>
@@ -14767,7 +14767,7 @@
         <v>138</v>
       </c>
       <c r="B130" s="23" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C130" s="25">
         <v>8190</v>
@@ -14808,7 +14808,7 @@
         <v>139</v>
       </c>
       <c r="B131" s="23" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C131" s="25">
         <v>5965</v>
@@ -14849,7 +14849,7 @@
         <v>140</v>
       </c>
       <c r="B132" s="23" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C132" s="25">
         <v>3930</v>
@@ -14890,7 +14890,7 @@
         <v>141</v>
       </c>
       <c r="B133" s="23" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C133" s="25">
         <v>8835</v>
@@ -14931,7 +14931,7 @@
         <v>142</v>
       </c>
       <c r="B134" s="23" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C134" s="25">
         <v>9800</v>
@@ -14972,7 +14972,7 @@
         <v>143</v>
       </c>
       <c r="B135" s="23" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C135" s="25">
         <v>7030</v>
@@ -15013,7 +15013,7 @@
         <v>144</v>
       </c>
       <c r="B136" s="23" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="C136" s="25">
         <v>6540</v>
@@ -15054,7 +15054,7 @@
         <v>145</v>
       </c>
       <c r="B137" s="23" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="C137" s="25">
         <v>5115</v>
@@ -15095,7 +15095,7 @@
         <v>146</v>
       </c>
       <c r="B138" s="23" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="C138" s="25">
         <v>8555</v>
@@ -15136,7 +15136,7 @@
         <v>147</v>
       </c>
       <c r="B139" s="23" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C139" s="25">
         <v>8295</v>
@@ -15177,7 +15177,7 @@
         <v>148</v>
       </c>
       <c r="B140" s="23" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="C140" s="25">
         <v>7205</v>
@@ -15218,7 +15218,7 @@
         <v>149</v>
       </c>
       <c r="B141" s="23" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C141" s="25">
         <v>5055</v>
@@ -15259,7 +15259,7 @@
         <v>150</v>
       </c>
       <c r="B142" s="23" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C142" s="25">
         <v>8140</v>
@@ -15300,7 +15300,7 @@
         <v>151</v>
       </c>
       <c r="B143" s="23" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C143" s="25">
         <v>9850</v>
@@ -15341,7 +15341,7 @@
         <v>152</v>
       </c>
       <c r="B144" s="23" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C144" s="25">
         <v>5625</v>
@@ -15382,7 +15382,7 @@
         <v>153</v>
       </c>
       <c r="B145" s="23" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C145" s="25">
         <v>6995</v>
@@ -15423,7 +15423,7 @@
         <v>154</v>
       </c>
       <c r="B146" s="23" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="C146" s="25">
         <v>7695</v>
@@ -15464,7 +15464,7 @@
         <v>155</v>
       </c>
       <c r="B147" s="23" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C147" s="25">
         <v>6930</v>
@@ -15505,7 +15505,7 @@
         <v>156</v>
       </c>
       <c r="B148" s="23" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C148" s="25">
         <v>7425</v>
@@ -15546,7 +15546,7 @@
         <v>157</v>
       </c>
       <c r="B149" s="23" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="C149" s="25">
         <v>3360</v>
@@ -15587,7 +15587,7 @@
         <v>158</v>
       </c>
       <c r="B150" s="23" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C150" s="25">
         <v>9275</v>
@@ -15628,7 +15628,7 @@
         <v>159</v>
       </c>
       <c r="B151" s="23" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C151" s="25">
         <v>11920</v>
@@ -15669,7 +15669,7 @@
         <v>160</v>
       </c>
       <c r="B152" s="23" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C152" s="25">
         <v>7875</v>
@@ -15710,7 +15710,7 @@
         <v>161</v>
       </c>
       <c r="B153" s="23" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C153" s="25">
         <v>13330</v>
@@ -15751,7 +15751,7 @@
         <v>162</v>
       </c>
       <c r="B154" s="23" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C154" s="25">
         <v>7620</v>
@@ -15792,7 +15792,7 @@
         <v>163</v>
       </c>
       <c r="B155" s="23" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C155" s="25">
         <v>12490</v>
@@ -15833,7 +15833,7 @@
         <v>164</v>
       </c>
       <c r="B156" s="23" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C156" s="25">
         <v>17070</v>
@@ -15874,7 +15874,7 @@
         <v>165</v>
       </c>
       <c r="B157" s="23" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C157" s="25">
         <v>16555</v>
@@ -15915,7 +15915,7 @@
         <v>166</v>
       </c>
       <c r="B158" s="23" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C158" s="25">
         <v>18780</v>
@@ -15956,7 +15956,7 @@
         <v>167</v>
       </c>
       <c r="B159" s="23" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C159" s="25">
         <v>14630</v>
@@ -15997,7 +15997,7 @@
         <v>168</v>
       </c>
       <c r="B160" s="23" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="C160" s="25">
         <v>11095</v>
@@ -16038,7 +16038,7 @@
         <v>169</v>
       </c>
       <c r="B161" s="23" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C161" s="25">
         <v>10585</v>
@@ -16079,7 +16079,7 @@
         <v>170</v>
       </c>
       <c r="B162" s="23" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C162" s="25">
         <v>7465</v>
@@ -16120,7 +16120,7 @@
         <v>171</v>
       </c>
       <c r="B163" s="23" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C163" s="25">
         <v>10230</v>
@@ -16161,7 +16161,7 @@
         <v>172</v>
       </c>
       <c r="B164" s="23" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C164" s="25">
         <v>5250</v>
@@ -16202,7 +16202,7 @@
         <v>173</v>
       </c>
       <c r="B165" s="23" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="C165" s="25">
         <v>9435</v>
@@ -16243,7 +16243,7 @@
         <v>174</v>
       </c>
       <c r="B166" s="23" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C166" s="25">
         <v>13200</v>
@@ -16282,7 +16282,7 @@
     <row r="167" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A167" s="11"/>
       <c r="B167" s="12" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C167" s="13">
         <v>1160895</v>
@@ -16342,7 +16342,7 @@
     <row r="1" spans="1:42" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="10"/>
       <c r="B1" s="1" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="2"/>
@@ -16352,73 +16352,73 @@
       <c r="H1" s="2"/>
     </row>
     <row r="2" spans="1:42" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="41" t="s">
-        <v>188</v>
-      </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
+      <c r="A2" s="42" t="s">
+        <v>180</v>
+      </c>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
     </row>
     <row r="3" spans="1:42" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="40" t="s">
-        <v>189</v>
-      </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
+      <c r="A3" s="41" t="s">
+        <v>181</v>
+      </c>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
     </row>
     <row r="4" spans="1:42" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="40" t="s">
-        <v>184</v>
-      </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
+      <c r="A4" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
     </row>
     <row r="5" spans="1:42" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="40" t="s">
-        <v>187</v>
-      </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
+      <c r="A5" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
     </row>
     <row r="6" spans="1:42" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="40" t="s">
-        <v>190</v>
-      </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
+      <c r="A6" s="41" t="s">
+        <v>182</v>
+      </c>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
       <c r="I6" s="6"/>
     </row>
     <row r="7" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="21" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="B7" s="20"/>
       <c r="C7" s="20"/>
@@ -16487,28 +16487,28 @@
     </row>
     <row r="9" spans="1:42" ht="29" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E9" s="33" t="s">
         <v>0</v>
       </c>
       <c r="F9" s="32" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G9" s="33" t="s">
         <v>1</v>
       </c>
       <c r="H9" s="32" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="I9" s="33" t="s">
         <v>2</v>
@@ -16519,7 +16519,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C10" s="24">
         <v>33300</v>
@@ -16548,7 +16548,7 @@
         <v>2</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C11" s="25">
         <v>31330</v>
@@ -16577,7 +16577,7 @@
         <v>3</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C12" s="25">
         <v>9855</v>
@@ -16606,7 +16606,7 @@
         <v>4</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C13" s="25">
         <v>10380</v>
@@ -16635,7 +16635,7 @@
         <v>5</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C14" s="25">
         <v>9360</v>
@@ -16664,7 +16664,7 @@
         <v>6</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C15" s="25">
         <v>21995</v>
@@ -16693,7 +16693,7 @@
         <v>7</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C16" s="25">
         <v>22445</v>
@@ -16722,7 +16722,7 @@
         <v>8</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C17" s="25">
         <v>10020</v>
@@ -16751,7 +16751,7 @@
         <v>9</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C18" s="25">
         <v>15200</v>
@@ -16780,7 +16780,7 @@
         <v>10</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C19" s="25">
         <v>11170</v>
@@ -16809,7 +16809,7 @@
         <v>11</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C20" s="25">
         <v>18470</v>
@@ -16838,7 +16838,7 @@
         <v>12</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C21" s="25">
         <v>10370</v>
@@ -16867,7 +16867,7 @@
         <v>13</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C22" s="25">
         <v>11865</v>
@@ -16896,7 +16896,7 @@
         <v>15</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C23" s="25">
         <v>8855</v>
@@ -16925,7 +16925,7 @@
         <v>16</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C24" s="25">
         <v>25645</v>
@@ -16954,7 +16954,7 @@
         <v>18</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C25" s="25">
         <v>11355</v>
@@ -16983,7 +16983,7 @@
         <v>19</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C26" s="25">
         <v>11370</v>
@@ -17012,7 +17012,7 @@
         <v>20</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C27" s="25">
         <v>12590</v>
@@ -17041,7 +17041,7 @@
         <v>21</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C28" s="25">
         <v>12180</v>
@@ -17070,7 +17070,7 @@
         <v>22</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C29" s="25">
         <v>16955</v>
@@ -17099,7 +17099,7 @@
         <v>23</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C30" s="25">
         <v>11285</v>
@@ -17128,7 +17128,7 @@
         <v>24</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C31" s="25">
         <v>21150</v>
@@ -17157,7 +17157,7 @@
         <v>25</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C32" s="25">
         <v>30040</v>
@@ -17186,7 +17186,7 @@
         <v>27</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C33" s="25">
         <v>28245</v>
@@ -17215,7 +17215,7 @@
         <v>28</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C34" s="25">
         <v>9385</v>
@@ -17244,7 +17244,7 @@
         <v>29</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C35" s="25">
         <v>9855</v>
@@ -17273,7 +17273,7 @@
         <v>30</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C36" s="25">
         <v>17510</v>
@@ -17302,7 +17302,7 @@
         <v>31</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C37" s="25">
         <v>16640</v>
@@ -17331,7 +17331,7 @@
         <v>32</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C38" s="25">
         <v>21300</v>
@@ -17360,7 +17360,7 @@
         <v>33</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C39" s="25">
         <v>17620</v>
@@ -17389,7 +17389,7 @@
         <v>34</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C40" s="25">
         <v>15960</v>
@@ -17418,7 +17418,7 @@
         <v>35</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C41" s="25">
         <v>25860</v>
@@ -17447,7 +17447,7 @@
         <v>36</v>
       </c>
       <c r="B42" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C42" s="25">
         <v>23800</v>
@@ -17476,7 +17476,7 @@
         <v>37</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C43" s="25">
         <v>17015</v>
@@ -17505,7 +17505,7 @@
         <v>38</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C44" s="25">
         <v>15905</v>
@@ -17534,7 +17534,7 @@
         <v>39</v>
       </c>
       <c r="B45" s="23" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C45" s="25">
         <v>22140</v>
@@ -17563,7 +17563,7 @@
         <v>40</v>
       </c>
       <c r="B46" s="23" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C46" s="25">
         <v>16955</v>
@@ -17592,7 +17592,7 @@
         <v>41</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C47" s="25">
         <v>8945</v>
@@ -17621,7 +17621,7 @@
         <v>42</v>
       </c>
       <c r="B48" s="23" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C48" s="25">
         <v>27155</v>
@@ -17650,7 +17650,7 @@
         <v>43</v>
       </c>
       <c r="B49" s="23" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C49" s="25">
         <v>17365</v>
@@ -17679,7 +17679,7 @@
         <v>44</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C50" s="25">
         <v>22520</v>
@@ -17708,7 +17708,7 @@
         <v>46</v>
       </c>
       <c r="B51" s="23" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C51" s="25">
         <v>15210</v>
@@ -17737,7 +17737,7 @@
         <v>47</v>
       </c>
       <c r="B52" s="23" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C52" s="25">
         <v>26760</v>
@@ -17766,7 +17766,7 @@
         <v>48</v>
       </c>
       <c r="B53" s="23" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C53" s="25">
         <v>16345</v>
@@ -17795,7 +17795,7 @@
         <v>49</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C54" s="25">
         <v>12085</v>
@@ -17824,7 +17824,7 @@
         <v>50</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C55" s="25">
         <v>15350</v>
@@ -17853,7 +17853,7 @@
         <v>52</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C56" s="25">
         <v>22330</v>
@@ -17882,7 +17882,7 @@
         <v>53</v>
       </c>
       <c r="B57" s="23" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C57" s="25">
         <v>19835</v>
@@ -17911,7 +17911,7 @@
         <v>54</v>
       </c>
       <c r="B58" s="23" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C58" s="25">
         <v>18390</v>
@@ -17940,7 +17940,7 @@
         <v>55</v>
       </c>
       <c r="B59" s="23" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C59" s="25">
         <v>20385</v>
@@ -17969,7 +17969,7 @@
         <v>56</v>
       </c>
       <c r="B60" s="23" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C60" s="25">
         <v>16530</v>
@@ -17998,7 +17998,7 @@
         <v>57</v>
       </c>
       <c r="B61" s="23" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C61" s="25">
         <v>10965</v>
@@ -18027,7 +18027,7 @@
         <v>58</v>
       </c>
       <c r="B62" s="23" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C62" s="25">
         <v>9150</v>
@@ -18056,7 +18056,7 @@
         <v>59</v>
       </c>
       <c r="B63" s="23" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C63" s="25">
         <v>17075</v>
@@ -18085,7 +18085,7 @@
         <v>60</v>
       </c>
       <c r="B64" s="23" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C64" s="25">
         <v>7905</v>
@@ -18114,7 +18114,7 @@
         <v>61</v>
       </c>
       <c r="B65" s="23" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C65" s="25">
         <v>15025</v>
@@ -18143,7 +18143,7 @@
         <v>62</v>
       </c>
       <c r="B66" s="23" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C66" s="25">
         <v>21830</v>
@@ -18172,7 +18172,7 @@
         <v>63</v>
       </c>
       <c r="B67" s="23" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C67" s="25">
         <v>21495</v>
@@ -18201,7 +18201,7 @@
         <v>64</v>
       </c>
       <c r="B68" s="23" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C68" s="25">
         <v>12195</v>
@@ -18230,7 +18230,7 @@
         <v>65</v>
       </c>
       <c r="B69" s="23" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C69" s="25">
         <v>14090</v>
@@ -18259,7 +18259,7 @@
         <v>66</v>
       </c>
       <c r="B70" s="23" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C70" s="25">
         <v>9310</v>
@@ -18288,7 +18288,7 @@
         <v>67</v>
       </c>
       <c r="B71" s="23" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C71" s="25">
         <v>7680</v>
@@ -18317,7 +18317,7 @@
         <v>68</v>
       </c>
       <c r="B72" s="23" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C72" s="25">
         <v>11305</v>
@@ -18346,7 +18346,7 @@
         <v>69</v>
       </c>
       <c r="B73" s="23" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C73" s="25">
         <v>7480</v>
@@ -18375,7 +18375,7 @@
         <v>70</v>
       </c>
       <c r="B74" s="23" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C74" s="25">
         <v>27815</v>
@@ -18404,7 +18404,7 @@
         <v>71</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C75" s="25">
         <v>11015</v>
@@ -18433,7 +18433,7 @@
         <v>72</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C76" s="25">
         <v>12760</v>
@@ -18462,7 +18462,7 @@
         <v>73</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C77" s="25">
         <v>21475</v>
@@ -18491,7 +18491,7 @@
         <v>74</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C78" s="25">
         <v>18535</v>
@@ -18520,7 +18520,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C79" s="25">
         <v>18130</v>
@@ -18549,7 +18549,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C80" s="25">
         <v>6435</v>
@@ -18578,7 +18578,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C81" s="25">
         <v>13110</v>
@@ -18607,7 +18607,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C82" s="25">
         <v>15425</v>
@@ -18636,7 +18636,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="23" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C83" s="25">
         <v>11195</v>
@@ -18665,7 +18665,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="23" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C84" s="25">
         <v>15465</v>
@@ -18694,7 +18694,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="23" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C85" s="25">
         <v>20500</v>
@@ -18723,7 +18723,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="23" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C86" s="25">
         <v>14620</v>
@@ -18752,7 +18752,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="23" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C87" s="25">
         <v>22675</v>
@@ -18781,7 +18781,7 @@
         <v>88</v>
       </c>
       <c r="B88" s="23" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C88" s="25">
         <v>21855</v>
@@ -18810,7 +18810,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="23" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C89" s="25">
         <v>10115</v>
@@ -18839,7 +18839,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="23" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C90" s="25">
         <v>14035</v>
@@ -18868,7 +18868,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="23" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C91" s="25">
         <v>10670</v>
@@ -18897,7 +18897,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="23" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C92" s="25">
         <v>13195</v>
@@ -18926,7 +18926,7 @@
         <v>94</v>
       </c>
       <c r="B93" s="23" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C93" s="25">
         <v>12820</v>
@@ -18955,7 +18955,7 @@
         <v>95</v>
       </c>
       <c r="B94" s="23" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C94" s="25">
         <v>29320</v>
@@ -18984,7 +18984,7 @@
         <v>96</v>
       </c>
       <c r="B95" s="23" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C95" s="25">
         <v>11250</v>
@@ -19013,7 +19013,7 @@
         <v>97</v>
       </c>
       <c r="B96" s="23" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C96" s="25">
         <v>12950</v>
@@ -19042,7 +19042,7 @@
         <v>98</v>
       </c>
       <c r="B97" s="23" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C97" s="25">
         <v>20070</v>
@@ -19071,7 +19071,7 @@
         <v>99</v>
       </c>
       <c r="B98" s="23" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C98" s="25">
         <v>16365</v>
@@ -19100,7 +19100,7 @@
         <v>100</v>
       </c>
       <c r="B99" s="23" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C99" s="25">
         <v>12420</v>
@@ -19129,7 +19129,7 @@
         <v>101</v>
       </c>
       <c r="B100" s="23" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C100" s="25">
         <v>10900</v>
@@ -19158,7 +19158,7 @@
         <v>102</v>
       </c>
       <c r="B101" s="23" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C101" s="25">
         <v>12285</v>
@@ -19187,7 +19187,7 @@
         <v>103</v>
       </c>
       <c r="B102" s="23" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C102" s="25">
         <v>14955</v>
@@ -19216,7 +19216,7 @@
         <v>105</v>
       </c>
       <c r="B103" s="23" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C103" s="25">
         <v>14690</v>
@@ -19245,7 +19245,7 @@
         <v>106</v>
       </c>
       <c r="B104" s="23" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C104" s="25">
         <v>13845</v>
@@ -19274,7 +19274,7 @@
         <v>107</v>
       </c>
       <c r="B105" s="23" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C105" s="25">
         <v>20720</v>
@@ -19303,7 +19303,7 @@
         <v>108</v>
       </c>
       <c r="B106" s="23" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C106" s="25">
         <v>14575</v>
@@ -19332,7 +19332,7 @@
         <v>109</v>
       </c>
       <c r="B107" s="23" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C107" s="25">
         <v>10025</v>
@@ -19361,7 +19361,7 @@
         <v>110</v>
       </c>
       <c r="B108" s="23" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C108" s="25">
         <v>11395</v>
@@ -19390,7 +19390,7 @@
         <v>111</v>
       </c>
       <c r="B109" s="23" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C109" s="25">
         <v>22235</v>
@@ -19419,7 +19419,7 @@
         <v>112</v>
       </c>
       <c r="B110" s="23" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C110" s="25">
         <v>6265</v>
@@ -19448,7 +19448,7 @@
         <v>113</v>
       </c>
       <c r="B111" s="23" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C111" s="25">
         <v>18685</v>
@@ -19477,7 +19477,7 @@
         <v>114</v>
       </c>
       <c r="B112" s="23" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C112" s="25">
         <v>7975</v>
@@ -19506,7 +19506,7 @@
         <v>115</v>
       </c>
       <c r="B113" s="23" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="C113" s="25">
         <v>13055</v>
@@ -19535,7 +19535,7 @@
         <v>116</v>
       </c>
       <c r="B114" s="23" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C114" s="25">
         <v>22790</v>
@@ -19564,7 +19564,7 @@
         <v>118</v>
       </c>
       <c r="B115" s="23" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C115" s="25">
         <v>27220</v>
@@ -19593,7 +19593,7 @@
         <v>119</v>
       </c>
       <c r="B116" s="23" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C116" s="25">
         <v>28335</v>
@@ -19622,7 +19622,7 @@
         <v>120</v>
       </c>
       <c r="B117" s="23" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C117" s="25">
         <v>26850</v>
@@ -19651,7 +19651,7 @@
         <v>121</v>
       </c>
       <c r="B118" s="23" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C118" s="25">
         <v>13695</v>
@@ -19680,7 +19680,7 @@
         <v>122</v>
       </c>
       <c r="B119" s="23" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C119" s="25">
         <v>22690</v>
@@ -19709,7 +19709,7 @@
         <v>123</v>
       </c>
       <c r="B120" s="23" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C120" s="25">
         <v>16135</v>
@@ -19738,7 +19738,7 @@
         <v>124</v>
       </c>
       <c r="B121" s="23" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C121" s="25">
         <v>17130</v>
@@ -19767,7 +19767,7 @@
         <v>125</v>
       </c>
       <c r="B122" s="23" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C122" s="25">
         <v>13375</v>
@@ -19796,7 +19796,7 @@
         <v>126</v>
       </c>
       <c r="B123" s="23" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C123" s="25">
         <v>24295</v>
@@ -19825,7 +19825,7 @@
         <v>128</v>
       </c>
       <c r="B124" s="23" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C124" s="25">
         <v>24160</v>
@@ -19854,7 +19854,7 @@
         <v>129</v>
       </c>
       <c r="B125" s="23" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C125" s="25">
         <v>27545</v>
@@ -19883,7 +19883,7 @@
         <v>130</v>
       </c>
       <c r="B126" s="23" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C126" s="25">
         <v>23975</v>
@@ -19912,7 +19912,7 @@
         <v>133</v>
       </c>
       <c r="B127" s="23" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C127" s="25">
         <v>13405</v>
@@ -19941,7 +19941,7 @@
         <v>134</v>
       </c>
       <c r="B128" s="23" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C128" s="25">
         <v>12610</v>
@@ -19970,7 +19970,7 @@
         <v>135</v>
       </c>
       <c r="B129" s="23" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C129" s="25">
         <v>17665</v>
@@ -19999,7 +19999,7 @@
         <v>136</v>
       </c>
       <c r="B130" s="23" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C130" s="25">
         <v>28145</v>
@@ -20028,7 +20028,7 @@
         <v>138</v>
       </c>
       <c r="B131" s="23" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C131" s="25">
         <v>22530</v>
@@ -20057,7 +20057,7 @@
         <v>139</v>
       </c>
       <c r="B132" s="23" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C132" s="25">
         <v>16525</v>
@@ -20086,7 +20086,7 @@
         <v>140</v>
       </c>
       <c r="B133" s="23" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C133" s="25">
         <v>9675</v>
@@ -20115,7 +20115,7 @@
         <v>141</v>
       </c>
       <c r="B134" s="23" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C134" s="25">
         <v>27055</v>
@@ -20144,7 +20144,7 @@
         <v>142</v>
       </c>
       <c r="B135" s="23" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C135" s="25">
         <v>26640</v>
@@ -20173,7 +20173,7 @@
         <v>143</v>
       </c>
       <c r="B136" s="23" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C136" s="25">
         <v>20670</v>
@@ -20202,7 +20202,7 @@
         <v>144</v>
       </c>
       <c r="B137" s="23" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="C137" s="25">
         <v>24935</v>
@@ -20231,7 +20231,7 @@
         <v>145</v>
       </c>
       <c r="B138" s="23" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="C138" s="25">
         <v>17325</v>
@@ -20260,7 +20260,7 @@
         <v>146</v>
       </c>
       <c r="B139" s="23" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="C139" s="25">
         <v>26095</v>
@@ -20289,7 +20289,7 @@
         <v>147</v>
       </c>
       <c r="B140" s="23" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C140" s="25">
         <v>21525</v>
@@ -20318,7 +20318,7 @@
         <v>148</v>
       </c>
       <c r="B141" s="23" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="C141" s="25">
         <v>21500</v>
@@ -20347,7 +20347,7 @@
         <v>149</v>
       </c>
       <c r="B142" s="23" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C142" s="25">
         <v>13925</v>
@@ -20376,7 +20376,7 @@
         <v>150</v>
       </c>
       <c r="B143" s="23" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C143" s="25">
         <v>20550</v>
@@ -20405,7 +20405,7 @@
         <v>151</v>
       </c>
       <c r="B144" s="23" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C144" s="25">
         <v>20175</v>
@@ -20434,7 +20434,7 @@
         <v>152</v>
       </c>
       <c r="B145" s="23" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C145" s="25">
         <v>15470</v>
@@ -20463,7 +20463,7 @@
         <v>153</v>
       </c>
       <c r="B146" s="23" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C146" s="25">
         <v>13790</v>
@@ -20492,7 +20492,7 @@
         <v>154</v>
       </c>
       <c r="B147" s="23" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="C147" s="25">
         <v>21375</v>
@@ -20521,7 +20521,7 @@
         <v>155</v>
       </c>
       <c r="B148" s="23" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C148" s="25">
         <v>18015</v>
@@ -20550,7 +20550,7 @@
         <v>156</v>
       </c>
       <c r="B149" s="23" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C149" s="25">
         <v>18675</v>
@@ -20579,7 +20579,7 @@
         <v>157</v>
       </c>
       <c r="B150" s="23" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="C150" s="25">
         <v>10730</v>
@@ -20608,7 +20608,7 @@
         <v>158</v>
       </c>
       <c r="B151" s="23" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C151" s="25">
         <v>23480</v>
@@ -20637,7 +20637,7 @@
         <v>159</v>
       </c>
       <c r="B152" s="23" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C152" s="25">
         <v>23590</v>
@@ -20666,7 +20666,7 @@
         <v>160</v>
       </c>
       <c r="B153" s="23" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C153" s="25">
         <v>17050</v>
@@ -20695,7 +20695,7 @@
         <v>161</v>
       </c>
       <c r="B154" s="23" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C154" s="25">
         <v>22610</v>
@@ -20724,7 +20724,7 @@
         <v>162</v>
       </c>
       <c r="B155" s="23" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C155" s="25">
         <v>13065</v>
@@ -20753,7 +20753,7 @@
         <v>163</v>
       </c>
       <c r="B156" s="23" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C156" s="25">
         <v>20010</v>
@@ -20782,7 +20782,7 @@
         <v>164</v>
       </c>
       <c r="B157" s="23" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C157" s="25">
         <v>25570</v>
@@ -20811,7 +20811,7 @@
         <v>165</v>
       </c>
       <c r="B158" s="23" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C158" s="25">
         <v>28135</v>
@@ -20840,7 +20840,7 @@
         <v>166</v>
       </c>
       <c r="B159" s="23" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C159" s="25">
         <v>31265</v>
@@ -20869,7 +20869,7 @@
         <v>167</v>
       </c>
       <c r="B160" s="23" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C160" s="25">
         <v>22200</v>
@@ -20898,7 +20898,7 @@
         <v>168</v>
       </c>
       <c r="B161" s="23" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="C161" s="25">
         <v>17820</v>
@@ -20927,7 +20927,7 @@
         <v>169</v>
       </c>
       <c r="B162" s="23" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C162" s="25">
         <v>16680</v>
@@ -20956,7 +20956,7 @@
         <v>170</v>
       </c>
       <c r="B163" s="23" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C163" s="25">
         <v>12640</v>
@@ -20985,7 +20985,7 @@
         <v>171</v>
       </c>
       <c r="B164" s="23" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C164" s="25">
         <v>23230</v>
@@ -21014,7 +21014,7 @@
         <v>172</v>
       </c>
       <c r="B165" s="23" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C165" s="25">
         <v>12315</v>
@@ -21043,7 +21043,7 @@
         <v>173</v>
       </c>
       <c r="B166" s="23" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="C166" s="25">
         <v>15880</v>
@@ -21072,7 +21072,7 @@
         <v>174</v>
       </c>
       <c r="B167" s="23" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C167" s="25">
         <v>22720</v>
@@ -21099,7 +21099,7 @@
     <row r="168" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A168" s="11"/>
       <c r="B168" s="12" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C168" s="13">
         <v>2761290</v>
@@ -21151,7 +21151,7 @@
     <row r="1" spans="1:50" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="10"/>
       <c r="B1" s="1" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -21194,19 +21194,19 @@
       <c r="AX1" s="7"/>
     </row>
     <row r="2" spans="1:50" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="40" t="s">
-        <v>188</v>
-      </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
+      <c r="A2" s="41" t="s">
+        <v>180</v>
+      </c>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
       <c r="U2" s="3"/>
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
@@ -21239,18 +21239,18 @@
       <c r="AX2" s="16"/>
     </row>
     <row r="3" spans="1:50" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="40" t="s">
-        <v>191</v>
-      </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
+      <c r="A3" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
       <c r="K3" s="18"/>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
@@ -21284,18 +21284,18 @@
       <c r="AX3" s="16"/>
     </row>
     <row r="4" spans="1:50" x14ac:dyDescent="0.2">
-      <c r="A4" s="40" t="s">
-        <v>184</v>
-      </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
+      <c r="A4" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
       <c r="K4" s="18"/>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
@@ -21329,18 +21329,18 @@
       <c r="AX4" s="16"/>
     </row>
     <row r="5" spans="1:50" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="40" t="s">
-        <v>187</v>
-      </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="40"/>
+      <c r="A5" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
       <c r="K5" s="18"/>
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
@@ -21375,7 +21375,7 @@
     </row>
     <row r="6" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A6" s="19" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
@@ -21420,7 +21420,7 @@
     </row>
     <row r="7" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
@@ -21465,7 +21465,7 @@
     </row>
     <row r="8" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="21" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="B8" s="20"/>
       <c r="C8" s="20"/>
@@ -21553,25 +21553,25 @@
     </row>
     <row r="10" spans="1:50" ht="29" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>182</v>
-      </c>
-      <c r="C10" s="42" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="42" t="s">
-        <v>18</v>
+        <v>174</v>
+      </c>
+      <c r="C10" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="40" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:50" x14ac:dyDescent="0.2">
@@ -21579,7 +21579,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C11" s="24">
         <v>10665</v>
@@ -21602,7 +21602,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C12" s="25">
         <v>9745</v>
@@ -21625,7 +21625,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C13" s="25">
         <v>3255</v>
@@ -21648,7 +21648,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C14" s="25">
         <v>3945</v>
@@ -21671,7 +21671,7 @@
         <v>5</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C15" s="25">
         <v>3195</v>
@@ -21694,7 +21694,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C16" s="25">
         <v>7775</v>
@@ -21717,7 +21717,7 @@
         <v>7</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C17" s="25">
         <v>8600</v>
@@ -21740,7 +21740,7 @@
         <v>8</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C18" s="25">
         <v>4105</v>
@@ -21763,7 +21763,7 @@
         <v>9</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C19" s="25">
         <v>6295</v>
@@ -21786,7 +21786,7 @@
         <v>10</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C20" s="25">
         <v>3885</v>
@@ -21809,7 +21809,7 @@
         <v>11</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C21" s="25">
         <v>6855</v>
@@ -21832,7 +21832,7 @@
         <v>12</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C22" s="25">
         <v>4220</v>
@@ -21855,7 +21855,7 @@
         <v>13</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C23" s="25">
         <v>4730</v>
@@ -21878,7 +21878,7 @@
         <v>15</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C24" s="25">
         <v>3475</v>
@@ -21901,7 +21901,7 @@
         <v>16</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C25" s="25">
         <v>10515</v>
@@ -21924,7 +21924,7 @@
         <v>18</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C26" s="25">
         <v>5280</v>
@@ -21947,7 +21947,7 @@
         <v>19</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C27" s="25">
         <v>5290</v>
@@ -21970,7 +21970,7 @@
         <v>20</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C28" s="25">
         <v>4785</v>
@@ -21993,7 +21993,7 @@
         <v>21</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C29" s="25">
         <v>3925</v>
@@ -22016,7 +22016,7 @@
         <v>22</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C30" s="25">
         <v>5670</v>
@@ -22039,7 +22039,7 @@
         <v>23</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C31" s="25">
         <v>3920</v>
@@ -22062,7 +22062,7 @@
         <v>24</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C32" s="25">
         <v>7225</v>
@@ -22085,7 +22085,7 @@
         <v>25</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C33" s="25">
         <v>9995</v>
@@ -22108,7 +22108,7 @@
         <v>27</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C34" s="25">
         <v>10355</v>
@@ -22131,7 +22131,7 @@
         <v>28</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C35" s="25">
         <v>3535</v>
@@ -22154,7 +22154,7 @@
         <v>29</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C36" s="25">
         <v>3590</v>
@@ -22177,7 +22177,7 @@
         <v>30</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C37" s="25">
         <v>6405</v>
@@ -22200,7 +22200,7 @@
         <v>31</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C38" s="25">
         <v>6820</v>
@@ -22223,7 +22223,7 @@
         <v>32</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C39" s="25">
         <v>8175</v>
@@ -22246,7 +22246,7 @@
         <v>33</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C40" s="25">
         <v>7155</v>
@@ -22269,7 +22269,7 @@
         <v>34</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C41" s="25">
         <v>6065</v>
@@ -22292,7 +22292,7 @@
         <v>35</v>
       </c>
       <c r="B42" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C42" s="25">
         <v>10035</v>
@@ -22315,7 +22315,7 @@
         <v>36</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C43" s="25">
         <v>9080</v>
@@ -22338,7 +22338,7 @@
         <v>37</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C44" s="25">
         <v>7830</v>
@@ -22361,7 +22361,7 @@
         <v>38</v>
       </c>
       <c r="B45" s="23" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C45" s="25">
         <v>6545</v>
@@ -22384,7 +22384,7 @@
         <v>39</v>
       </c>
       <c r="B46" s="23" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C46" s="25">
         <v>8345</v>
@@ -22407,7 +22407,7 @@
         <v>40</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C47" s="25">
         <v>6355</v>
@@ -22430,7 +22430,7 @@
         <v>41</v>
       </c>
       <c r="B48" s="23" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C48" s="25">
         <v>3305</v>
@@ -22453,7 +22453,7 @@
         <v>42</v>
       </c>
       <c r="B49" s="23" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C49" s="25">
         <v>12235</v>
@@ -22476,7 +22476,7 @@
         <v>43</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C50" s="25">
         <v>7260</v>
@@ -22499,7 +22499,7 @@
         <v>44</v>
       </c>
       <c r="B51" s="23" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C51" s="25">
         <v>8200</v>
@@ -22522,7 +22522,7 @@
         <v>46</v>
       </c>
       <c r="B52" s="23" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C52" s="25">
         <v>5450</v>
@@ -22545,7 +22545,7 @@
         <v>47</v>
       </c>
       <c r="B53" s="23" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C53" s="25">
         <v>10255</v>
@@ -22568,7 +22568,7 @@
         <v>48</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C54" s="25">
         <v>6385</v>
@@ -22591,7 +22591,7 @@
         <v>49</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C55" s="25">
         <v>4755</v>
@@ -22614,7 +22614,7 @@
         <v>50</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C56" s="25">
         <v>6165</v>
@@ -22637,7 +22637,7 @@
         <v>52</v>
       </c>
       <c r="B57" s="23" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C57" s="25">
         <v>10460</v>
@@ -22660,7 +22660,7 @@
         <v>53</v>
       </c>
       <c r="B58" s="23" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C58" s="25">
         <v>8500</v>
@@ -22683,7 +22683,7 @@
         <v>54</v>
       </c>
       <c r="B59" s="23" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C59" s="25">
         <v>7460</v>
@@ -22706,7 +22706,7 @@
         <v>55</v>
       </c>
       <c r="B60" s="23" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C60" s="25">
         <v>7060</v>
@@ -22729,7 +22729,7 @@
         <v>56</v>
       </c>
       <c r="B61" s="23" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C61" s="25">
         <v>6425</v>
@@ -22752,7 +22752,7 @@
         <v>57</v>
       </c>
       <c r="B62" s="23" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C62" s="25">
         <v>5275</v>
@@ -22775,7 +22775,7 @@
         <v>58</v>
       </c>
       <c r="B63" s="23" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C63" s="25">
         <v>3730</v>
@@ -22798,7 +22798,7 @@
         <v>59</v>
       </c>
       <c r="B64" s="23" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C64" s="25">
         <v>6935</v>
@@ -22821,7 +22821,7 @@
         <v>60</v>
       </c>
       <c r="B65" s="23" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C65" s="25">
         <v>3375</v>
@@ -22844,7 +22844,7 @@
         <v>61</v>
       </c>
       <c r="B66" s="23" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C66" s="25">
         <v>6005</v>
@@ -22867,7 +22867,7 @@
         <v>62</v>
       </c>
       <c r="B67" s="23" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C67" s="25">
         <v>9520</v>
@@ -22890,7 +22890,7 @@
         <v>63</v>
       </c>
       <c r="B68" s="23" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C68" s="25">
         <v>9430</v>
@@ -22913,7 +22913,7 @@
         <v>64</v>
       </c>
       <c r="B69" s="23" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C69" s="25">
         <v>5230</v>
@@ -22936,7 +22936,7 @@
         <v>65</v>
       </c>
       <c r="B70" s="23" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C70" s="25">
         <v>6040</v>
@@ -22959,7 +22959,7 @@
         <v>66</v>
       </c>
       <c r="B71" s="23" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C71" s="25">
         <v>3915</v>
@@ -22982,7 +22982,7 @@
         <v>67</v>
       </c>
       <c r="B72" s="23" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C72" s="25">
         <v>3635</v>
@@ -23005,7 +23005,7 @@
         <v>68</v>
       </c>
       <c r="B73" s="23" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C73" s="25">
         <v>4880</v>
@@ -23028,7 +23028,7 @@
         <v>69</v>
       </c>
       <c r="B74" s="23" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C74" s="25">
         <v>3110</v>
@@ -23051,7 +23051,7 @@
         <v>70</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C75" s="25">
         <v>12705</v>
@@ -23074,7 +23074,7 @@
         <v>71</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C76" s="25">
         <v>6190</v>
@@ -23097,7 +23097,7 @@
         <v>72</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C77" s="25">
         <v>6110</v>
@@ -23120,7 +23120,7 @@
         <v>73</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C78" s="25">
         <v>13290</v>
@@ -23143,7 +23143,7 @@
         <v>74</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C79" s="25">
         <v>9530</v>
@@ -23166,7 +23166,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C80" s="25">
         <v>9515</v>
@@ -23189,7 +23189,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C81" s="25">
         <v>3240</v>
@@ -23212,7 +23212,7 @@
         <v>80</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C82" s="25">
         <v>6195</v>
@@ -23235,7 +23235,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="23" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C83" s="25">
         <v>6835</v>
@@ -23258,7 +23258,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="23" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C84" s="25">
         <v>5260</v>
@@ -23281,7 +23281,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="23" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C85" s="25">
         <v>7880</v>
@@ -23304,7 +23304,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="23" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C86" s="25">
         <v>11295</v>
@@ -23327,7 +23327,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="23" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C87" s="25">
         <v>6790</v>
@@ -23350,7 +23350,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="23" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C88" s="25">
         <v>10470</v>
@@ -23373,7 +23373,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="23" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C89" s="25">
         <v>11110</v>
@@ -23396,7 +23396,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="23" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C90" s="25">
         <v>3840</v>
@@ -23419,7 +23419,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="23" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C91" s="25">
         <v>6030</v>
@@ -23442,7 +23442,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="23" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C92" s="25">
         <v>4190</v>
@@ -23465,7 +23465,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="23" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C93" s="25">
         <v>5215</v>
@@ -23488,7 +23488,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="23" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C94" s="25">
         <v>5775</v>
@@ -23511,7 +23511,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="23" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C95" s="25">
         <v>16320</v>
@@ -23534,7 +23534,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="23" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C96" s="25">
         <v>5815</v>
@@ -23557,7 +23557,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="23" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C97" s="25">
         <v>7210</v>
@@ -23580,7 +23580,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="23" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C98" s="25">
         <v>9880</v>
@@ -23603,7 +23603,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="23" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C99" s="25">
         <v>7150</v>
@@ -23626,7 +23626,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="23" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C100" s="25">
         <v>6000</v>
@@ -23649,7 +23649,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="23" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C101" s="25">
         <v>5070</v>
@@ -23672,7 +23672,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="23" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C102" s="25">
         <v>5245</v>
@@ -23695,7 +23695,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="23" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C103" s="25">
         <v>5785</v>
@@ -23718,7 +23718,7 @@
         <v>105</v>
       </c>
       <c r="B104" s="23" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C104" s="25">
         <v>5465</v>
@@ -23741,7 +23741,7 @@
         <v>106</v>
       </c>
       <c r="B105" s="23" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C105" s="25">
         <v>6345</v>
@@ -23764,7 +23764,7 @@
         <v>107</v>
       </c>
       <c r="B106" s="23" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C106" s="25">
         <v>8635</v>
@@ -23787,7 +23787,7 @@
         <v>108</v>
       </c>
       <c r="B107" s="23" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C107" s="25">
         <v>5925</v>
@@ -23810,7 +23810,7 @@
         <v>109</v>
       </c>
       <c r="B108" s="23" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C108" s="25">
         <v>3695</v>
@@ -23833,7 +23833,7 @@
         <v>110</v>
       </c>
       <c r="B109" s="23" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C109" s="25">
         <v>4400</v>
@@ -23856,7 +23856,7 @@
         <v>111</v>
       </c>
       <c r="B110" s="23" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C110" s="25">
         <v>9020</v>
@@ -23879,7 +23879,7 @@
         <v>112</v>
       </c>
       <c r="B111" s="23" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C111" s="25">
         <v>2570</v>
@@ -23902,7 +23902,7 @@
         <v>113</v>
       </c>
       <c r="B112" s="23" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C112" s="25">
         <v>7925</v>
@@ -23925,7 +23925,7 @@
         <v>114</v>
       </c>
       <c r="B113" s="23" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C113" s="25">
         <v>3105</v>
@@ -23948,7 +23948,7 @@
         <v>115</v>
       </c>
       <c r="B114" s="23" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="C114" s="25">
         <v>5060</v>
@@ -23971,7 +23971,7 @@
         <v>116</v>
       </c>
       <c r="B115" s="23" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C115" s="25">
         <v>7860</v>
@@ -23994,7 +23994,7 @@
         <v>118</v>
       </c>
       <c r="B116" s="23" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C116" s="25">
         <v>10355</v>
@@ -24017,7 +24017,7 @@
         <v>119</v>
       </c>
       <c r="B117" s="23" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C117" s="25">
         <v>10255</v>
@@ -24040,7 +24040,7 @@
         <v>120</v>
       </c>
       <c r="B118" s="23" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C118" s="25">
         <v>9390</v>
@@ -24063,7 +24063,7 @@
         <v>121</v>
       </c>
       <c r="B119" s="23" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C119" s="25">
         <v>5300</v>
@@ -24086,7 +24086,7 @@
         <v>122</v>
       </c>
       <c r="B120" s="23" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C120" s="25">
         <v>9630</v>
@@ -24109,7 +24109,7 @@
         <v>123</v>
       </c>
       <c r="B121" s="23" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C121" s="25">
         <v>5875</v>
@@ -24132,7 +24132,7 @@
         <v>124</v>
       </c>
       <c r="B122" s="23" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C122" s="25">
         <v>6575</v>
@@ -24155,7 +24155,7 @@
         <v>125</v>
       </c>
       <c r="B123" s="23" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C123" s="25">
         <v>4970</v>
@@ -24178,7 +24178,7 @@
         <v>126</v>
       </c>
       <c r="B124" s="23" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C124" s="25">
         <v>8720</v>
@@ -24201,7 +24201,7 @@
         <v>128</v>
       </c>
       <c r="B125" s="23" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C125" s="25">
         <v>8910</v>
@@ -24224,7 +24224,7 @@
         <v>129</v>
       </c>
       <c r="B126" s="23" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C126" s="25">
         <v>9095</v>
@@ -24247,7 +24247,7 @@
         <v>130</v>
       </c>
       <c r="B127" s="23" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C127" s="25">
         <v>7600</v>
@@ -24270,7 +24270,7 @@
         <v>133</v>
       </c>
       <c r="B128" s="23" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C128" s="25">
         <v>4420</v>
@@ -24293,7 +24293,7 @@
         <v>134</v>
       </c>
       <c r="B129" s="23" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C129" s="25">
         <v>3785</v>
@@ -24316,7 +24316,7 @@
         <v>135</v>
       </c>
       <c r="B130" s="23" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C130" s="25">
         <v>5890</v>
@@ -24339,7 +24339,7 @@
         <v>136</v>
       </c>
       <c r="B131" s="23" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C131" s="25">
         <v>10155</v>
@@ -24362,7 +24362,7 @@
         <v>138</v>
       </c>
       <c r="B132" s="23" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C132" s="25">
         <v>8220</v>
@@ -24385,7 +24385,7 @@
         <v>139</v>
       </c>
       <c r="B133" s="23" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C133" s="25">
         <v>5955</v>
@@ -24408,7 +24408,7 @@
         <v>140</v>
       </c>
       <c r="B134" s="23" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C134" s="25">
         <v>3945</v>
@@ -24431,7 +24431,7 @@
         <v>141</v>
       </c>
       <c r="B135" s="23" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C135" s="25">
         <v>8805</v>
@@ -24454,7 +24454,7 @@
         <v>142</v>
       </c>
       <c r="B136" s="23" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C136" s="25">
         <v>9825</v>
@@ -24477,7 +24477,7 @@
         <v>143</v>
       </c>
       <c r="B137" s="23" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C137" s="25">
         <v>7000</v>
@@ -24500,7 +24500,7 @@
         <v>144</v>
       </c>
       <c r="B138" s="23" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="C138" s="25">
         <v>6535</v>
@@ -24523,7 +24523,7 @@
         <v>145</v>
       </c>
       <c r="B139" s="23" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="C139" s="25">
         <v>5095</v>
@@ -24546,7 +24546,7 @@
         <v>146</v>
       </c>
       <c r="B140" s="23" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="C140" s="25">
         <v>8540</v>
@@ -24569,7 +24569,7 @@
         <v>147</v>
       </c>
       <c r="B141" s="23" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C141" s="25">
         <v>8295</v>
@@ -24592,7 +24592,7 @@
         <v>148</v>
       </c>
       <c r="B142" s="23" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="C142" s="25">
         <v>7200</v>
@@ -24615,7 +24615,7 @@
         <v>149</v>
       </c>
       <c r="B143" s="23" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C143" s="25">
         <v>5050</v>
@@ -24638,7 +24638,7 @@
         <v>150</v>
       </c>
       <c r="B144" s="23" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C144" s="25">
         <v>8160</v>
@@ -24661,7 +24661,7 @@
         <v>151</v>
       </c>
       <c r="B145" s="23" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C145" s="25">
         <v>9830</v>
@@ -24684,7 +24684,7 @@
         <v>152</v>
       </c>
       <c r="B146" s="23" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C146" s="25">
         <v>5625</v>
@@ -24707,7 +24707,7 @@
         <v>153</v>
       </c>
       <c r="B147" s="23" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C147" s="25">
         <v>6990</v>
@@ -24730,7 +24730,7 @@
         <v>154</v>
       </c>
       <c r="B148" s="23" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="C148" s="25">
         <v>7665</v>
@@ -24753,7 +24753,7 @@
         <v>155</v>
       </c>
       <c r="B149" s="23" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C149" s="25">
         <v>6970</v>
@@ -24776,7 +24776,7 @@
         <v>156</v>
       </c>
       <c r="B150" s="23" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C150" s="25">
         <v>7420</v>
@@ -24799,7 +24799,7 @@
         <v>157</v>
       </c>
       <c r="B151" s="23" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="C151" s="25">
         <v>3360</v>
@@ -24822,7 +24822,7 @@
         <v>158</v>
       </c>
       <c r="B152" s="23" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C152" s="25">
         <v>9280</v>
@@ -24845,7 +24845,7 @@
         <v>159</v>
       </c>
       <c r="B153" s="23" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C153" s="25">
         <v>11930</v>
@@ -24868,7 +24868,7 @@
         <v>160</v>
       </c>
       <c r="B154" s="23" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C154" s="25">
         <v>7880</v>
@@ -24891,7 +24891,7 @@
         <v>161</v>
       </c>
       <c r="B155" s="23" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C155" s="25">
         <v>13330</v>
@@ -24914,7 +24914,7 @@
         <v>162</v>
       </c>
       <c r="B156" s="23" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C156" s="25">
         <v>7700</v>
@@ -24937,7 +24937,7 @@
         <v>163</v>
       </c>
       <c r="B157" s="23" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C157" s="25">
         <v>12405</v>
@@ -24960,7 +24960,7 @@
         <v>164</v>
       </c>
       <c r="B158" s="23" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C158" s="25">
         <v>17070</v>
@@ -24983,7 +24983,7 @@
         <v>165</v>
       </c>
       <c r="B159" s="23" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C159" s="25">
         <v>16540</v>
@@ -25006,7 +25006,7 @@
         <v>166</v>
       </c>
       <c r="B160" s="23" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C160" s="25">
         <v>18790</v>
@@ -25029,7 +25029,7 @@
         <v>167</v>
       </c>
       <c r="B161" s="23" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C161" s="25">
         <v>14660</v>
@@ -25052,7 +25052,7 @@
         <v>168</v>
       </c>
       <c r="B162" s="23" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="C162" s="25">
         <v>11055</v>
@@ -25075,7 +25075,7 @@
         <v>169</v>
       </c>
       <c r="B163" s="23" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C163" s="25">
         <v>10585</v>
@@ -25098,7 +25098,7 @@
         <v>170</v>
       </c>
       <c r="B164" s="23" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C164" s="25">
         <v>7455</v>
@@ -25121,7 +25121,7 @@
         <v>171</v>
       </c>
       <c r="B165" s="23" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C165" s="25">
         <v>10190</v>
@@ -25144,7 +25144,7 @@
         <v>172</v>
       </c>
       <c r="B166" s="23" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C166" s="25">
         <v>5315</v>
@@ -25167,7 +25167,7 @@
         <v>173</v>
       </c>
       <c r="B167" s="23" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="C167" s="25">
         <v>9430</v>
@@ -25190,7 +25190,7 @@
         <v>174</v>
       </c>
       <c r="B168" s="23" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C168" s="25">
         <v>13195</v>
@@ -25211,7 +25211,7 @@
     <row r="169" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A169" s="11"/>
       <c r="B169" s="12" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C169" s="13">
         <v>1160890</v>
